--- a/Analises/Financas/Rascunho_aula_cambial.xlsx
+++ b/Analises/Financas/Rascunho_aula_cambial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transferoswiss-my.sharepoint.com/personal/thiago_cunha_transfero_com/Documents/Documents/GitHub/Portfolio/Analises/Financas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43E3CAD-CD52-4B52-AF86-123FFC93EA2F}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF193840-0F7E-4861-B2DB-919CD1B43172}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1502479B-278D-479A-8AB5-81E13C922CC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
   <si>
     <t>dólar spot</t>
   </si>
@@ -480,20 +480,67 @@
   <si>
     <t>Contexto: vamos provar, com números, que um swap cambial entrega a exposição ao dólar menos o custo de juros — ou seja, é um dólar comprado "a prazo, financiado".</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exercício 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Separando as quatro taxas (e não caindo na ambiguidade)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exercício 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — O ganho (e o risco) do carry-trade</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="0.0000%"/>
-    <numFmt numFmtId="167" formatCode="0.00000%"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="0.000000000"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.00000000_-;\-* #,##0.00000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="182" formatCode="0.0000000%"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="0.0000%"/>
+    <numFmt numFmtId="166" formatCode="0.00000%"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.000000000"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.00000000_-;\-* #,##0.00000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0000000%"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;???_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -717,55 +764,55 @@
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="182" fontId="1" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="1" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="5" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -783,6 +830,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1605,7 +1656,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="33" t="s">
+      <c r="A59" s="32" t="s">
         <v>66</v>
       </c>
       <c r="B59" t="s">
@@ -1613,7 +1664,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="34" t="s">
+      <c r="A60" s="33" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1746,7 +1797,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>85</v>
       </c>
@@ -1758,7 +1809,7 @@
       <c r="G15" s="29"/>
       <c r="H15" s="29"/>
     </row>
-    <row r="16" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>86</v>
       </c>
@@ -1770,7 +1821,7 @@
       <c r="G16" s="29"/>
       <c r="H16" s="29"/>
     </row>
-    <row r="17" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>87</v>
       </c>
@@ -1782,7 +1833,7 @@
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
     </row>
-    <row r="18" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>88</v>
       </c>
@@ -1809,7 +1860,7 @@
       <c r="J20" s="27"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="31" t="s">
         <v>91</v>
       </c>
       <c r="B22" t="s">
@@ -1833,77 +1884,72 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4F0CE4-25CA-42FF-8949-99746E9D32AD}">
-  <dimension ref="A1:XEY35"/>
+  <dimension ref="A1:XFD50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="16379" max="16379" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="16379" max="16379" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="16381" max="16384" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>95</v>
       </c>
-      <c r="XEY1" s="9">
-        <v>7705</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
-      <c r="XEY2" s="9">
-        <f>XEY1*6</f>
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
-      <c r="A3" s="39" t="s">
+      <c r="XEY1" s="9"/>
+    </row>
+    <row r="2" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="XEY2" s="9"/>
+    </row>
+    <row r="3" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
-      <c r="A4" s="40">
+    <row r="4" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="A4" s="39">
         <v>20000</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="41">
         <f>A4*50000</f>
         <v>1000000000</v>
       </c>
-      <c r="XEY4" s="10">
-        <f>XEY1/2</f>
-        <v>3852.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
-      <c r="A5" s="40">
+      <c r="XEY4" s="10"/>
+    </row>
+    <row r="5" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="A5" s="39">
         <v>50000</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="41">
         <f t="shared" ref="B5:B6" si="0">A5*50000</f>
         <v>2500000000</v>
       </c>
-      <c r="XEY5" s="10">
-        <f>XEY1*0.3</f>
-        <v>2311.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
-      <c r="A6" s="40">
+      <c r="XEY5" s="10"/>
+    </row>
+    <row r="6" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="A6" s="39">
         <v>550000</v>
       </c>
-      <c r="B6" s="42">
+      <c r="B6" s="41">
         <f t="shared" si="0"/>
         <v>27500000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+      <c r="XEY6" s="10"/>
+    </row>
+    <row r="7" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="XEY7" s="10"/>
+    </row>
+    <row r="8" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+      <c r="XEY8" s="9"/>
+    </row>
+    <row r="9" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>98</v>
       </c>
@@ -1911,28 +1957,39 @@
         <f>20000*50000</f>
         <v>1000000000</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="42">
         <f>B9-1000000000</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>99</v>
       </c>
       <c r="B11" s="19"/>
-    </row>
-    <row r="13" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+      <c r="XEZ11" s="1"/>
+    </row>
+    <row r="12" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
+      <c r="XEY12" s="9"/>
+      <c r="XEZ12" s="9"/>
+      <c r="XFA12" s="9"/>
+      <c r="XFB12" s="9"/>
+      <c r="XFC12" s="9"/>
+      <c r="XFD12" s="9"/>
+    </row>
+    <row r="13" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+      <c r="XEY13" s="43"/>
+    </row>
+    <row r="14" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="15" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+      <c r="XEY14" s="43"/>
+    </row>
+    <row r="15" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>104</v>
       </c>
@@ -1940,7 +1997,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:3 16379:16379" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3 16379:16384" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -1956,7 +2013,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="36">
         <f>5.4675-5.4</f>
         <v>6.7499999999999893E-2</v>
       </c>
@@ -1989,11 +2046,11 @@
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="35">
+      <c r="A26" s="34">
         <f>A25*A24-1</f>
         <v>1.2345679012345734E-2</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="35" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2003,48 +2060,48 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="38" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
+      <c r="A30" s="38">
         <v>1</v>
       </c>
-      <c r="B30" s="39">
+      <c r="B30" s="38">
         <v>5.4675000000000002</v>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="37">
         <f>(5.4/B30)*(1+0.025) - 1</f>
         <v>1.2345679012345734E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="39">
+      <c r="A31" s="38">
         <v>2</v>
       </c>
-      <c r="B31" s="39">
+      <c r="B31" s="38">
         <v>5.49</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="37">
         <f>(5.4/B31)*(1+0.025) - 1</f>
         <v>8.1967213114753079E-3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="39">
+      <c r="A32" s="38">
         <v>3</v>
       </c>
-      <c r="B32" s="39">
+      <c r="B32" s="38">
         <v>5.52</v>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="37">
         <f>(5.4/B32)*(1+0.025) - 1</f>
         <v>2.7173913043478937E-3</v>
       </c>
@@ -2057,6 +2114,16 @@
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Analises/Financas/Rascunho_aula_cambial.xlsx
+++ b/Analises/Financas/Rascunho_aula_cambial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transferoswiss-my.sharepoint.com/personal/thiago_cunha_transfero_com/Documents/Documents/GitHub/Portfolio/Analises/Financas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF193840-0F7E-4861-B2DB-919CD1B43172}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B116A43A-F803-4665-87B1-803C546B8DC1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1502479B-278D-479A-8AB5-81E13C922CC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="174">
   <si>
     <t>dólar spot</t>
   </si>
@@ -526,12 +526,357 @@
       <t xml:space="preserve"> — O ganho (e o risco) do carry-trade</t>
     </r>
   </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>Dados de 1 contrato swap (ponta comprada em dolar)</t>
+  </si>
+  <si>
+    <t>1 contrato = tamanho = $ 50k</t>
+  </si>
+  <si>
+    <t>Juros acumulados no periodo</t>
+  </si>
+  <si>
+    <t>Liquidando em reais...</t>
+  </si>
+  <si>
+    <t>Notional*(variacao_dolar - DI)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Calculando resultado nos Cenários A e B:</t>
+    </r>
+  </si>
+  <si>
+    <t>A: dolar sobe 5%</t>
+  </si>
+  <si>
+    <t>B: dolar cai 5%</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_f </t>
+  </si>
+  <si>
+    <t>contrato:</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>ponta dolar</t>
+  </si>
+  <si>
+    <t>ponta real</t>
+  </si>
+  <si>
+    <t>net_pt_dol R$</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">b) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Comparando com compra spot dolar (caminhos A e B):</t>
+    </r>
+  </si>
+  <si>
+    <t>i_BR = 14,25%  -&gt;  juro em real
+i_US =  3,65%  -&gt;  juro do dólar lá fora
+S    = 5,00   -&gt;  dólar à vista
+F    = 5,50   -&gt;  dólar futuro de 1 ano</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cupom cambial</t>
+    </r>
+  </si>
+  <si>
+    <t>i_br</t>
+  </si>
+  <si>
+    <t>i_eua</t>
+  </si>
+  <si>
+    <t>(1+i_br)*S = (1+i_cc)*F -&gt; i_cc = (1+i_br)*S/F - 1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">b) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diferencial bruto e foward premium</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">db </t>
+  </si>
+  <si>
+    <t>premium</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contexto:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Você toma dólar barato, aplica em real caro e não trava o forward. Vamos ver de quanto é a aposta</t>
+    </r>
+  </si>
+  <si>
+    <t>empréstimo</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>i_eua_a.a</t>
+  </si>
+  <si>
+    <t>i_br_a.a</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>resultado final BR</t>
+  </si>
+  <si>
+    <t>F = 5</t>
+  </si>
+  <si>
+    <t>F=5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C </t>
+  </si>
+  <si>
+    <t>F=6</t>
+  </si>
+  <si>
+    <t>divida final US</t>
+  </si>
+  <si>
+    <t>Resultado Bruto</t>
+  </si>
+  <si>
+    <t>Rentabilidade</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Calculando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lucro em dolares</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> achar cambio de breakeven (F que zera o lucro)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ou seja, caso o cambio seja 5.5113 no futuro</t>
+  </si>
+  <si>
+    <t>ele paga a divida apenas</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Diferença (física -swap)</t>
+    </r>
+  </si>
+  <si>
+    <t>Evidentemente é a mesma coisa que manter 250k no DI</t>
+  </si>
+  <si>
+    <t>Ou seja, o swap é a variação do dola + carrego DI (você paga o custo de oportunidade de não comprar dolar no spot)</t>
+  </si>
+  <si>
+    <t>Quero comprar 250k R$ em dolar, mas n quero me descapitalizar. Você quer me vender esses dolares, mas não é bobo. Diz "n quer descapitalizar? Tudo bem. Te garanto esses dolares no dia tal, mas quero o DI". Eu digo ok.</t>
+  </si>
+  <si>
+    <t>Perceba</t>
+  </si>
+  <si>
+    <t>eu te devo</t>
+  </si>
+  <si>
+    <t>você me deve</t>
+  </si>
+  <si>
+    <t>se dolar subir</t>
+  </si>
+  <si>
+    <t>se cair, eu passo a te dever mais isso</t>
+  </si>
+  <si>
+    <t>Ao chegar no prazo acordado, ao invés de trocarmos dolar por real, trocamos apenas reais de acordo com a movimentação do dolar</t>
+  </si>
+  <si>
+    <t>Ou vc me passa</t>
+  </si>
+  <si>
+    <t>Ou eu te passo</t>
+  </si>
+  <si>
+    <t>Perceba que se o dolar subir, eu ganho a valorização do dolar mas pago o DI. Se o dolar cair eu perco a desvalorização e ainda pago o DI</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="11">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
@@ -540,7 +885,9 @@
     <numFmt numFmtId="168" formatCode="0.000000000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.00000000_-;\-* #,##0.00000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="0.0000000%"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;???_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;???_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -762,7 +1109,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
@@ -812,7 +1159,13 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1884,11 +2237,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4F0CE4-25CA-42FF-8949-99746E9D32AD}">
-  <dimension ref="A1:XFD50"/>
+  <dimension ref="A1:XFD104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="16379" max="16379" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="16381" max="16384" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2106,27 +2463,543 @@
         <v>2.7173913043478937E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" s="9">
+        <f>50000*5</f>
+        <v>250000</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="45">
+        <f>2.5/100</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" t="s">
+        <v>130</v>
+      </c>
+      <c r="G43" t="s">
+        <v>131</v>
+      </c>
+      <c r="H43" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44">
+        <f xml:space="preserve"> 5*1.05</f>
+        <v>5.25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="43">
+        <f>B37*(0.05-0.025)</f>
+        <v>6250</v>
+      </c>
+      <c r="F44" s="9">
+        <f>B37*(C44/B38-1)</f>
+        <v>12500.000000000011</v>
+      </c>
+      <c r="G44" s="10">
+        <f>B37*(B39)</f>
+        <v>6250</v>
+      </c>
+      <c r="H44" s="10">
+        <f>F44-G44</f>
+        <v>6250.0000000000109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45">
+        <f>5*0.95</f>
+        <v>4.75</v>
+      </c>
+      <c r="D45" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="10">
+        <f>B37*(-0.05-0.025)</f>
+        <v>-18750.000000000004</v>
+      </c>
+      <c r="F45" s="9">
+        <f>B37*(C45/B38-1)</f>
+        <v>-12500.000000000011</v>
+      </c>
+      <c r="G45" s="10">
+        <f>B37*B39</f>
+        <v>6250</v>
+      </c>
+      <c r="H45" s="10">
+        <f>F45-G45</f>
+        <v>-18750.000000000011</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="9">
+        <f>B37/B38</f>
+        <v>50000</v>
+      </c>
+      <c r="C48" s="10">
+        <f>B48*C44</f>
+        <v>262500</v>
+      </c>
+      <c r="D48" s="10">
+        <f>C48-B37</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="9">
+        <f>B37/B38</f>
+        <v>50000</v>
+      </c>
+      <c r="C49" s="10">
+        <f>B49*C45</f>
+        <v>237500</v>
+      </c>
+      <c r="D49" s="10">
+        <f>C49-B37</f>
+        <v>-12500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="10">
+        <f>D48-H44</f>
+        <v>6249.9999999999891</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="10">
+        <f>D49-H45</f>
+        <v>6250.0000000000109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="10">
+        <f>B37*B39</f>
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>166</v>
+      </c>
+      <c r="B59" s="10">
+        <f>B37*B39</f>
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>167</v>
+      </c>
+      <c r="B60" s="9">
+        <f>(C44/B38- 1)*B37</f>
+        <v>12500.000000000011</v>
+      </c>
+      <c r="C60" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" s="9">
+        <f>(C45/B38 - 1)*B37</f>
+        <v>-12500.000000000011</v>
+      </c>
+      <c r="E60" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" s="10">
+        <f>B60-B59</f>
+        <v>6250.0000000000109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" s="10">
+        <f>D60-B59</f>
+        <v>-18750.000000000011</v>
+      </c>
+      <c r="F62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="64" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="46"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <f>14.25/100</f>
+        <v>0.14249999999999999</v>
+      </c>
+      <c r="B66" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <f>0.0365</f>
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="1">
+        <f>(1+A66)*(A68/A69) - 1</f>
+        <v>3.863636363636358E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5.5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="1">
+        <f>A66-A67</f>
+        <v>0.10599999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="1">
+        <f>A69/A68 - 1</f>
+        <v>0.10000000000000009</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>116</v>
       </c>
     </row>
+    <row r="77" spans="1:3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A77" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>144</v>
+      </c>
+      <c r="C84" t="s">
+        <v>145</v>
+      </c>
+      <c r="D84" t="s">
+        <v>146</v>
+      </c>
+      <c r="E84" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85">
+        <v>100</v>
+      </c>
+      <c r="C85">
+        <f>B85*B81</f>
+        <v>500</v>
+      </c>
+      <c r="D85">
+        <f>3.65/100</f>
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="E85">
+        <f>14.25/100</f>
+        <v>0.14249999999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>149</v>
+      </c>
+      <c r="B88">
+        <f>C85*(1+E85)</f>
+        <v>571.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>154</v>
+      </c>
+      <c r="B89">
+        <f>B85*(1+D85)</f>
+        <v>103.64999999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>126</v>
+      </c>
+      <c r="B92" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" s="47">
+        <f>B88/5 - B89</f>
+        <v>10.600000000000009</v>
+      </c>
+      <c r="D92" s="45">
+        <f>C92/B85</f>
+        <v>0.10600000000000008</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>129</v>
+      </c>
+      <c r="B93" t="s">
+        <v>151</v>
+      </c>
+      <c r="C93" s="47">
+        <f>B88/5.5 - B89</f>
+        <v>0.21363636363636829</v>
+      </c>
+      <c r="D93" s="1">
+        <f>C93/B85</f>
+        <v>2.1363636363636827E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="47">
+        <f>B88/6 - B89</f>
+        <v>-8.4416666666666629</v>
+      </c>
+      <c r="D94" s="1">
+        <f>C94/B85</f>
+        <v>-8.4416666666666626E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99">
+        <f>B88/B89</f>
+        <v>5.5113362276893394</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101">
+        <f>B88/B99</f>
+        <v>103.64999999999999</v>
+      </c>
+      <c r="C101" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A64:B64"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Analises/Financas/Rascunho_aula_cambial.xlsx
+++ b/Analises/Financas/Rascunho_aula_cambial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transferoswiss-my.sharepoint.com/personal/thiago_cunha_transfero_com/Documents/Documents/GitHub/Portfolio/Analises/Financas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="479" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B116A43A-F803-4665-87B1-803C546B8DC1}"/>
+  <xr:revisionPtr revIDLastSave="701" documentId="8_{196C2FF4-0DA8-4F9F-BFAA-2B5DF9350DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04386493-C9B3-4339-9E8D-14D1C00EB019}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1502479B-278D-479A-8AB5-81E13C922CC1}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="217">
   <si>
     <t>dólar spot</t>
   </si>
@@ -870,6 +870,360 @@
   </si>
   <si>
     <t>Perceba que se o dolar subir, eu ganho a valorização do dolar mas pago o DI. Se o dolar cair eu perco a desvalorização e ainda pago o DI</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exercício 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — Hedge cambial com SWAP</t>
+    </r>
+  </si>
+  <si>
+    <t>U$</t>
+  </si>
+  <si>
+    <t>Entrar em swap cambial ficando na ponta que paga a variação do dólar e recebe DI (dolar sintético vendido que cancela o dolar comprado)</t>
+  </si>
+  <si>
+    <t>Notional</t>
+  </si>
+  <si>
+    <t>Recebemos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A </t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>F/S - 1</t>
+  </si>
+  <si>
+    <t>ResultadoNET</t>
+  </si>
+  <si>
+    <t>Perceba que em cada caso:</t>
+  </si>
+  <si>
+    <t>dolar muda</t>
+  </si>
+  <si>
+    <t>contrato paga</t>
+  </si>
+  <si>
+    <t>resultado</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">que é o mesmo que se tivesse ficado na </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renda fixa</t>
+    </r>
+  </si>
+  <si>
+    <t>No entanto, se o dolar dispara mais</t>
+  </si>
+  <si>
+    <t>O contrato paga</t>
+  </si>
+  <si>
+    <t>Você passa a dever 28k</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Que, novamente, é o mesmo que se tivesse ficado na </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renda fixa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BR</t>
+    </r>
+  </si>
+  <si>
+    <t>Se o dolar cai</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <r>
+      <t>Que, novamente, é o mesmo que se tivesse ficado na</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> renda fixa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resutado_swap para F = 5, 5.5 , 6 e 4.5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exercicio 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - hedge cambial com futuros (WDO) e diferença para swap</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Entrar em futuro de dólar via Mini dolar (vale 10k USD por contrato cheio, enquanto DOL vale 50k). Para anular o 'comprado' de 100k USDs, o fundo </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vende</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> futuro.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tamanho WDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Quantos contratos WDO o fundo precisa vender para hedgear 100k USDs? (e quantos DOL cheios dariam o mesmo hedge?)</t>
+    </r>
+  </si>
+  <si>
+    <t>WDO</t>
+  </si>
+  <si>
+    <t>ou</t>
+  </si>
+  <si>
+    <t>2 contratos DOL</t>
+  </si>
+  <si>
+    <t>vendo 10 contratos</t>
+  </si>
+  <si>
+    <t>receberei no vencimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comprei </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultado </t>
+  </si>
+  <si>
+    <t>Perceba que em todos esses casos:</t>
+  </si>
+  <si>
+    <t>ativo</t>
+  </si>
+  <si>
+    <t>variacao_ativo</t>
+  </si>
+  <si>
+    <t>variacaoWDO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S_fim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 5, 5.50, 6 e 4.5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OBS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: existe diferença entre F como valor futuro previsto pelo mercado e S_fim como valor realizado no vencimento (no exercicio de swap utilizamos F como S_fim pois não fazia diferença, nossa exposição dependia do spot)</t>
+    </r>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>b)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> resultado de uma posição vendida em futuro, carregada até o vencimento:</t>
+    </r>
+  </si>
+  <si>
+    <t>Que é o equivalente precificado pelo mercado entre F/S no inicio de tudo para o rendimento desse dolar nesse tempo (notional * casado).</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1463,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
@@ -1166,6 +1520,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2237,13 +2592,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4F0CE4-25CA-42FF-8949-99746E9D32AD}">
-  <dimension ref="A1:XFD104"/>
+  <dimension ref="A1:XFD165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="16379" max="16379" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -2824,24 +3181,22 @@
         <v>0.10000000000000009</v>
       </c>
     </row>
-    <row r="76" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="77" spans="1:3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="79" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -2849,7 +3204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2857,7 +3212,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="84" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>144</v>
       </c>
@@ -2871,7 +3226,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>143</v>
       </c>
@@ -2891,7 +3246,7 @@
         <v>0.14249999999999999</v>
       </c>
     </row>
-    <row r="88" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>149</v>
       </c>
@@ -2900,7 +3255,7 @@
         <v>571.25</v>
       </c>
     </row>
-    <row r="89" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>154</v>
       </c>
@@ -2909,7 +3264,7 @@
         <v>103.64999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>155</v>
       </c>
@@ -2917,7 +3272,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="92" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>126</v>
       </c>
@@ -2933,7 +3288,7 @@
         <v>0.10600000000000008</v>
       </c>
     </row>
-    <row r="93" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>129</v>
       </c>
@@ -2949,7 +3304,7 @@
         <v>2.1363636363636827E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>152</v>
       </c>
@@ -2965,12 +3320,12 @@
         <v>-8.4416666666666626E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="99" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2979,12 +3334,12 @@
         <v>5.5113362276893394</v>
       </c>
     </row>
-    <row r="100" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="101" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B101">
         <f>B88/B99</f>
         <v>103.64999999999999</v>
@@ -2993,9 +3348,577 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>175</v>
+      </c>
+      <c r="B106" s="9">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109">
+        <v>0.14249999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" s="10">
+        <f>B106*B108</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>178</v>
+      </c>
+      <c r="B111" s="10">
+        <f>B110*B109</f>
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>178</v>
+      </c>
+      <c r="B112" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>195</v>
+      </c>
+      <c r="E113" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>179</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114" s="45">
+        <f>B114/B108-1</f>
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114" s="10">
+        <f>B111-D114</f>
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>129</v>
+      </c>
+      <c r="B115">
+        <v>5.5</v>
+      </c>
+      <c r="C115" s="45">
+        <f>B115/B108-1</f>
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="D115" s="10">
+        <f>B110*C115</f>
+        <v>50000.000000000044</v>
+      </c>
+      <c r="E115" s="10">
+        <f>B111-D115</f>
+        <v>21249.999999999956</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>180</v>
+      </c>
+      <c r="B116">
+        <v>6</v>
+      </c>
+      <c r="C116" s="45">
+        <f>B116/B108-1</f>
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="D116" s="10">
+        <f>C116*B110</f>
+        <v>99999.999999999971</v>
+      </c>
+      <c r="E116" s="10">
+        <f>B111-D116</f>
+        <v>-28749.999999999971</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>193</v>
+      </c>
+      <c r="B117">
+        <v>4.5</v>
+      </c>
+      <c r="C117" s="45">
+        <f>B117/B108-1</f>
+        <v>-9.9999999999999978E-2</v>
+      </c>
+      <c r="D117" s="10">
+        <f>C117*B110</f>
+        <v>-49999.999999999985</v>
+      </c>
+      <c r="E117" s="10">
+        <f>B111-D117</f>
+        <v>121249.99999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="10">
+        <f>B110</f>
+        <v>500000</v>
+      </c>
+      <c r="B120" s="10">
+        <f>B106*B115</f>
+        <v>550000</v>
+      </c>
+      <c r="C120" s="10">
+        <f>B120-A120</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>185</v>
+      </c>
+      <c r="B121" s="10">
+        <f>E115</f>
+        <v>21249.999999999956</v>
+      </c>
+      <c r="D121" s="9"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>186</v>
+      </c>
+      <c r="B122" s="10">
+        <f>B121+C120</f>
+        <v>71249.999999999956</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>187</v>
+      </c>
+      <c r="C123" s="10">
+        <f>B110*B109</f>
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="10">
+        <f>A120</f>
+        <v>500000</v>
+      </c>
+      <c r="B125" s="10">
+        <f>B116*B106</f>
+        <v>600000</v>
+      </c>
+      <c r="C125" s="10">
+        <f>B125-A125</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>189</v>
+      </c>
+      <c r="B126" s="10">
+        <f>E116</f>
+        <v>-28749.999999999971</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>186</v>
+      </c>
+      <c r="B128" s="10">
+        <f>B126+C125</f>
+        <v>71250.000000000029</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>191</v>
+      </c>
+      <c r="E129" s="10">
+        <f>B110*B109</f>
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="9">
+        <v>500000</v>
+      </c>
+      <c r="B131" s="10">
+        <f>B106*4.5</f>
+        <v>450000</v>
+      </c>
+      <c r="C131" s="10">
+        <f>B131-A131</f>
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>189</v>
+      </c>
+      <c r="B132" s="10">
+        <f>E117</f>
+        <v>121249.99999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>186</v>
+      </c>
+      <c r="B133" s="10">
+        <f>B132+C131</f>
+        <v>71249.999999999985</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>194</v>
+      </c>
+      <c r="E134" s="9">
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B137" s="9">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>3</v>
+      </c>
+      <c r="B139" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>198</v>
+      </c>
+      <c r="B140" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>199</v>
+      </c>
+      <c r="B141">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <f>B137/B140</f>
+        <v>10</v>
+      </c>
+      <c r="B144" t="s">
+        <v>75</v>
+      </c>
+      <c r="C144" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>202</v>
+      </c>
+      <c r="B145" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="9">
+        <f>A144*B140*(B141-B139)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>204</v>
+      </c>
+      <c r="B148" s="9"/>
+      <c r="C148" s="10"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>205</v>
+      </c>
+      <c r="B149" s="9">
+        <v>100000</v>
+      </c>
+      <c r="C149" s="10">
+        <v>5.5</v>
+      </c>
+      <c r="D149" s="9">
+        <f>B149*C149</f>
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>206</v>
+      </c>
+      <c r="B150" s="9">
+        <v>100000</v>
+      </c>
+      <c r="C150">
+        <v>5</v>
+      </c>
+      <c r="D150" s="10">
+        <f>B150*C150</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>207</v>
+      </c>
+      <c r="D151" s="10">
+        <f>D149-D150</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>212</v>
+      </c>
+      <c r="B153" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>5</v>
+      </c>
+      <c r="B154" s="44">
+        <f>$A$144*$B$140*($B$141-A154)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>5.5</v>
+      </c>
+      <c r="B155" s="44">
+        <f>$A$144*$B$140*($B$141-A155)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>6</v>
+      </c>
+      <c r="B156" s="44">
+        <f>$A$144*$B$140*($B$141-A156)</f>
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>4.5</v>
+      </c>
+      <c r="B157" s="44">
+        <f>$A$144*$B$140*($B$141-A157)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>209</v>
+      </c>
+      <c r="C160" t="s">
+        <v>210</v>
+      </c>
+      <c r="D160" t="s">
+        <v>211</v>
+      </c>
+      <c r="E160" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="9">
+        <f>B137*B139</f>
+        <v>500000</v>
+      </c>
+      <c r="B161" s="10">
+        <f>B137*A154</f>
+        <v>500000</v>
+      </c>
+      <c r="C161" s="10">
+        <f>B161-A161</f>
+        <v>0</v>
+      </c>
+      <c r="D161" s="48">
+        <f>B154</f>
+        <v>50000</v>
+      </c>
+      <c r="E161" s="43">
+        <f>C161+D161</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="9">
+        <v>500000</v>
+      </c>
+      <c r="B162" s="10">
+        <f>B137*A155</f>
+        <v>550000</v>
+      </c>
+      <c r="C162" s="10">
+        <f>B162-A162</f>
+        <v>50000</v>
+      </c>
+      <c r="D162" s="48">
+        <f>B155</f>
+        <v>0</v>
+      </c>
+      <c r="E162" s="43">
+        <f>C162+D162</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="9">
+        <v>500000</v>
+      </c>
+      <c r="B163" s="10">
+        <f>B137*A156</f>
+        <v>600000</v>
+      </c>
+      <c r="C163" s="10">
+        <f>B163-A163</f>
+        <v>100000</v>
+      </c>
+      <c r="D163" s="48">
+        <f>B156</f>
+        <v>-50000</v>
+      </c>
+      <c r="E163" s="43">
+        <f>C163+D163</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="9">
+        <v>500000</v>
+      </c>
+      <c r="B164" s="10">
+        <f>B137*A157</f>
+        <v>450000</v>
+      </c>
+      <c r="C164" s="10">
+        <f>B164-A164</f>
+        <v>-50000</v>
+      </c>
+      <c r="D164" s="48">
+        <f>B157</f>
+        <v>100000</v>
+      </c>
+      <c r="E164" s="43">
+        <f>C164+D164</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A64:B64"/>
